--- a/data/trans_dic/IP31KM05_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM05_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,24%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>68,68; 82,14</t>
+          <t>77,43; 90,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>77,57; 91,01</t>
+          <t>67,68; 81,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76,11; 85,1</t>
+          <t>75,06; 84,48</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,47%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>80,21; 89,31</t>
+          <t>83,07; 90,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>82,61; 90,49</t>
+          <t>80,54; 89,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82,98; 88,77</t>
+          <t>82,89; 88,84</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>73,3%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>67,75; 84,86</t>
+          <t>66,41; 78,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>65,22; 78,08</t>
+          <t>66,96; 78,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>68,6; 80,09</t>
+          <t>68,66; 77,72</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,53%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>79,12; 88,9</t>
+          <t>77,01; 87,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>75,61; 86,94</t>
+          <t>78,64; 89,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79,36; 86,8</t>
+          <t>79,97; 86,83</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,33%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>77,47; 83,75</t>
+          <t>79,69; 84,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>78,52; 84,14</t>
+          <t>77,33; 82,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>79,07; 83,23</t>
+          <t>79,42; 83,23</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>144</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>86034</t>
+          <t>104658</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>116611</t>
+          <t>89109</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>202645</t>
+          <t>193767</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>78466; 93845</t>
+          <t>95160; 111226</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>106124; 124514</t>
+          <t>80271; 96727</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>191083; 213655</t>
+          <t>181275; 204017</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>227</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>158740</t>
+          <t>202200</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>214390</t>
+          <t>153928</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>373130</t>
+          <t>356127</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>149284; 166220</t>
+          <t>192083; 210060</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>204475; 223970</t>
+          <t>145447; 161500</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>359829; 384952</t>
+          <t>341358; 365858</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>163</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>141817</t>
+          <t>121995</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>132228</t>
+          <t>113700</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>274046</t>
+          <t>235695</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>127546; 159742</t>
+          <t>110582; 130855</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>119405; 142950</t>
+          <t>103812; 122356</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>254752; 297395</t>
+          <t>220777; 249904</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>200</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>139686</t>
+          <t>137157</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>145531</t>
+          <t>138618</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>285217</t>
+          <t>275775</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>130172; 146262</t>
+          <t>127969; 145469</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>134057; 154147</t>
+          <t>128950; 146084</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>271283; 296714</t>
+          <t>264003; 286661</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>772</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>734</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>772</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>526278</t>
+          <t>566010</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>608760</t>
+          <t>495355</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1135038</t>
+          <t>1061364</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>506008; 547004</t>
+          <t>547310; 583530</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>584740; 626642</t>
+          <t>478057; 510739</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1105313; 1163495</t>
+          <t>1036479; 1086227</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM05_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM05_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que consumen pescados con regularidad (por lo menos 2-3 veces a la semana) (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>85,16%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>75,14%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>80,24%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>77,43; 90,5</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>67,68; 81,56</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>75,06; 84,48</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>87,44%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>85,23%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>86,47%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>83,07; 90,84</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>80,54; 89,43</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>82,89; 88,84</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>73,26%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>73,34%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>73,3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>66,41; 78,58</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>66,96; 78,92</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>68,66; 77,72</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>82,54%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>84,53%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>83,53%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>77,01; 87,54</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>78,64; 89,09</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>79,97; 86,83</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>82,41%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>80,13%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>81,33%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>79,69; 84,96</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>77,33; 82,62</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>79,42; 83,23</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.8515981926264042</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.7513517182991548</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.8023671639597938</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>104658</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>89109</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>193767</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.7743141325106566</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.6768284883171853</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.7506405322612733</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>95160; 111226</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>80271; 96727</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>181275; 204017</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.9050417500692485</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.8155837886298777</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.8448134902447976</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.8744122077194718</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.8523484724263329</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.8647370514018665</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>202200</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>153928</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>356127</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.8306625699310498</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.8053836330624954</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.8288756699965398</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>192083; 210060</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>145447; 161500</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>341358; 365858</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.908403854301485</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.8942786856493059</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.8883647940150257</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.7326076944413483</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.7333668755941737</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.7329737289915218</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>121995</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>113700</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>235695</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.6640699714947202</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.6695935311711</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.6865824663430803</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>110582; 130855</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>103812; 122356</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>220777; 249904</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.7858133614375555</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.7892006548547306</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.7771604701550503</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>395</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.8254255267866182</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.8453393540195601</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.8353165129108717</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>137157</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>138618</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>275775</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.7701349297374732</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.7863783391349985</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.7996599527524192</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>127969; 145469</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>128950; 146084</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>264003; 286661</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.8754491262389659</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.8908676374546729</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.8682908124803685</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>772</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>734</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1506</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.824097730611566</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.8012749870382651</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.8132863464772361</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>566010</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>495355</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1061364</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.7968715016082131</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.7732946395301733</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.7942181017584944</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>547310; 583530</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>478057; 510739</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1036479; 1086227</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.8496062956783793</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.8261601407413717</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.8323378662793819</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumen pescados con regularidad (por lo menos 2-3 veces a la semana) (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>139</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>144</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>104658</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>89109</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>193767</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>95160</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>80271</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>181275</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>111226</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>96727</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>204017</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>284</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>227</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>202200</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>153928</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>356127</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>192083</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>145447</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>341358</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>210060</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>161500</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>365858</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>154</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>163</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>121995</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>113700</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>235695</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>110582</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>103812</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>220777</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>130855</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>122356</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>249904</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>195</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>137157</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>138618</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>275775</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>127969</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>128950</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>264003</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>145469</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>146084</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>286661</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>772</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>734</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>566010</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>495355</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1061364</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>547310</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>478057</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>1036479</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>583530</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>510739</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>1086227</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>